--- a/sheets/대금율보/검수/억새풀.xlsx
+++ b/sheets/대금율보/검수/억새풀.xlsx
@@ -1968,20 +1968,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="57.14" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -1996,7 +1996,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="63.76" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="I3" s="22"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="63.76" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21" t="inlineStr">
         <is>
@@ -2062,7 +2062,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="23"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="63.76" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21"/>
       <c r="C5" s="23"/>
@@ -2073,7 +2073,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="23"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="63.76" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21"/>
       <c r="C6" s="24"/>
@@ -2084,7 +2084,7 @@
       <c r="H6" s="21"/>
       <c r="I6" s="24"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="63.76" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="25" t="inlineStr">
         <is>
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I7" s="22"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="63.76" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2150,7 +2150,7 @@
       <c r="H8" s="21"/>
       <c r="I8" s="23"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="63.76" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -2177,7 +2177,7 @@
       <c r="H9" s="21"/>
       <c r="I9" s="23"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="63.76" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="24"/>
@@ -2192,7 +2192,7 @@
       <c r="H10" s="21"/>
       <c r="I10" s="24"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="63.76" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -2226,7 +2226,7 @@
       </c>
       <c r="I11" s="22"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="63.76" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21" t="inlineStr">
         <is>
@@ -2260,7 +2260,7 @@
       </c>
       <c r="I12" s="23"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="63.76" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21" t="inlineStr">
         <is>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="I13" s="23"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="63.76" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -2328,7 +2328,7 @@
       </c>
       <c r="I14" s="24"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="63.76" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -2360,7 +2360,7 @@
       </c>
       <c r="I15" s="22"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="63.76" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21"/>
       <c r="C16" s="23"/>
@@ -2375,7 +2375,7 @@
       </c>
       <c r="I16" s="27"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="63.76" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21"/>
       <c r="C17" s="23"/>
@@ -2390,7 +2390,7 @@
       </c>
       <c r="I17" s="23"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="63.76" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -2420,6 +2420,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="70"/>
 </worksheet>
 </file>